--- a/AAII_Financials/Quarterly/TAP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TAP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="92">
   <si>
     <t>TAP</t>
   </si>
@@ -656,544 +656,557 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>3096500</v>
+      </c>
+      <c r="E8" s="3">
         <v>2351100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2662400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2973500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>3200800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2304100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2735600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3042700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3252300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2596400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2790800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3298400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3266600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2346300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2629500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2935200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2921700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2214600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2619200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2822700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2939400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1898400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2294300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2753500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2503400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2102800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2486200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2841600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2948300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2303300</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2418700</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2934200</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>3085200</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>2331500</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>2579600</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>2883200</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>3091300</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>2448700</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>2294000</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>947600</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2033200</v>
+      </c>
+      <c r="E9" s="3">
         <v>1453900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1694100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1800000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1918900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1453200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1698100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1840200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1922400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1632900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1757800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1952200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2047700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1575600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1705800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1951500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2101700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1286800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1761900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1629100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1667900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1167400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1399100</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1551000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1456600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1479000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1520000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1685400</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1759800</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1413000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1596000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1714000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>1739100</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>1535700</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>1519800</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>1592000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>1755500</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>1372300</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>1470000</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>541300</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1063300</v>
+      </c>
+      <c r="E10" s="3">
         <v>897200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>968300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1173500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1281900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>850900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1037500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1202500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1329900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>963500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1033000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1346200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1218900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>770700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>923700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>983700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>820000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>927800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>857300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1193600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1271500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>731000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>895200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1202500</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1046800</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>623800</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>966200</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1156200</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1188500</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>890300</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>822700</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1220200</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1346100</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>795800</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>1059800</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>1291200</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>1335800</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>1076400</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>824000</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>406300</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1236,8 +1249,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1358,8 +1372,11 @@
       <c r="AP12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1480,210 +1497,216 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>9100</v>
+      </c>
+      <c r="E14" s="3">
         <v>42500</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>3300</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>3920900</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-16300</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>20200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>42400</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>65200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-6300</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>149700</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>12700</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-200</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>500</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>860700</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-5300</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>600</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>26700</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>27200</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>-2600</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>9000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>10900</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>1529600</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>59600</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>64300</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>86600</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>49900</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>703300</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>-49900</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>13000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>18000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>36600</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>9500</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>-314800</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>8300</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>10200</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>16500</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>3800</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AP14" s="3">
         <v>-2321200</v>
       </c>
-      <c r="AP14" s="3">
+      <c r="AQ14" s="3">
         <v>-4900</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>171300</v>
+      </c>
+      <c r="E15" s="3">
         <v>183200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>175900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>179800</v>
       </c>
-      <c r="G15" s="3">
-        <v>152200</v>
-      </c>
       <c r="H15" s="3">
+        <v>170100</v>
+      </c>
+      <c r="I15" s="3">
         <v>162400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>153700</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>175400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>167700</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>169000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>207300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>168700</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>168400</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>171500</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>50800</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>51800</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>52200</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>53300</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>54700</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>54000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>54800</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>54500</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>55100</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>55400</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>54600</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>54900</v>
-      </c>
-      <c r="AC15" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AD15" s="3" t="s">
         <v>8</v>
@@ -1700,8 +1723,8 @@
       <c r="AH15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI15" s="3">
-        <v>0</v>
+      <c r="AI15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AJ15" s="3">
         <v>0</v>
@@ -1724,8 +1747,11 @@
       <c r="AP15" s="3">
         <v>0</v>
       </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1765,252 +1791,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2746700</v>
+      </c>
+      <c r="E17" s="3">
         <v>2059000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2301400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2483200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2608500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2072600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2304500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2552100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2643600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2280100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2438500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2696500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2780000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2188000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3141000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2605100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2807200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1990200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2454200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2291300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2358600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1721200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>3577000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2245200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2045400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2195300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2175300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>3078900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2479600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2081200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2277000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>2464500</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>2494300</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>1902000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>2309400</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>2377000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>2554400</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>2084300</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>-236700</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>658400</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>349800</v>
+      </c>
+      <c r="E18" s="3">
         <v>292100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>361000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>490300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>592300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>231500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>431100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>490600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>608700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>316300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>352300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>601900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>486600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>158300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-511500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>330100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>114500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>224400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>165000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>531400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>580800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>177200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-1282700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>508300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>458000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-92500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>310900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-237300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>468700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>222100</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>141700</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>469700</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>590900</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>429500</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>270200</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>506200</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>536900</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>364400</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>2530700</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>289200</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2053,297 +2086,304 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="E20" s="3">
         <v>-2700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>35200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>8900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-4800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-1600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-12200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-2300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>8800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-9000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-3600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-8900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-3200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-52600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-57100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-59600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-50700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-55500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-50800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-58200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-50900</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-54600</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-57900</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-56300</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-66200</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-100900</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-68400</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-65100</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-38000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>6500</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-59600</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-67900</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-72100</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>22300</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>5900</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>12500</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>13100</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>15200</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>524000</v>
+      </c>
+      <c r="E21" s="3">
         <v>478000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>501700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>661200</v>
       </c>
-      <c r="G21" s="3">
-        <v>749300</v>
-      </c>
       <c r="H21" s="3">
+        <v>767200</v>
+      </c>
+      <c r="I21" s="3">
         <v>395500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>597000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>665100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>778700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>476500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>568600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>774200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>663900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>333000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-394900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>443200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>226600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>347400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>291400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>680900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>724200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>328600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-1130200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>671100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>639400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>97800</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>427600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-94000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>620400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>397000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>361500</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>624700</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>738900</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>571100</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>501000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>720400</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>748300</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>574600</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>2730000</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>356600</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>60500</v>
+      </c>
+      <c r="E22" s="3">
         <v>60200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>62300</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>62700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>58500</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>61300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>63100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>106400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>51200</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>48400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>71500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>48800</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>54600</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>59100</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
-      </c>
       <c r="R22" s="3">
         <v>0</v>
       </c>
@@ -2359,8 +2399,8 @@
       <c r="V22" s="3">
         <v>0</v>
       </c>
-      <c r="W22" s="3" t="s">
-        <v>8</v>
+      <c r="W22" s="3">
+        <v>0</v>
       </c>
       <c r="X22" s="3" t="s">
         <v>8</v>
@@ -2377,23 +2417,23 @@
       <c r="AB22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AC22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD22" s="3">
         <v>3400</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>2900</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>3000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>2800</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>78900</v>
-      </c>
-      <c r="AH22" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AI22" s="3" t="s">
         <v>8</v>
@@ -2401,270 +2441,279 @@
       <c r="AJ22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AK22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL22" s="3">
         <v>90900</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>71600</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>89200</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>96600</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>90000</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>66600</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>283100</v>
+      </c>
+      <c r="E23" s="3">
         <v>194700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>266300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-3495500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>554900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>156300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>346300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>331400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>559900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>265400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>165500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>544000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>441100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>101900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-564100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>273000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>54900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>173700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>109500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>480600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>522600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>126300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-1337300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>450400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>401700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-158700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>206600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-308600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>400600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>181300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>69300</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>410100</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>523000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>357400</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>201600</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>440500</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>460200</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>280900</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>2455900</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>223400</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>61500</v>
+      </c>
+      <c r="E24" s="3">
         <v>44600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>57000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-558600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>130600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>33200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>52600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>102600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>134600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>55500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>60000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>112400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>95000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>28700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>25700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>54900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>7000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>36400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>27100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>26800</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>132300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>44300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>36600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>104000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>204500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-43300</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>40400</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>90700</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>70400</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>32200</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-6400</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>64500</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>92200</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>74900</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>23900</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>147400</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>125200</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>65900</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>997700</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>19600</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2785,252 +2834,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>221600</v>
+      </c>
+      <c r="E26" s="3">
         <v>150100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>209300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-2936900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>424300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>123100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>293700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>228800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>425300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>209900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>105500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>431600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>346100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>73200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-589800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>218100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>47900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>137300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>82400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>453800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>390300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>82000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-1373900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>346400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>197200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-115400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>166200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-399300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>330200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>149100</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>75700</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>345600</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>430800</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>282500</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>177700</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>293100</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>335000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>215000</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>1458200</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>203800</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>231700</v>
+      </c>
+      <c r="E27" s="3">
         <v>151300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>238300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-2927600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>428700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>121000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>287800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>199800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>427000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>207800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>103300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>430700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>342400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>72500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-590500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>216400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>47300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>151500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>80000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>453000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>388600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>84100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-1369800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>342800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>195000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-117000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>163700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-402800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>329400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>151400</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>76000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>338300</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>424100</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>278100</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>173200</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>287000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>329900</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>208500</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>1456000</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>202500</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3151,8 +3209,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3237,8 +3298,8 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-      <c r="AE29" s="3" t="s">
-        <v>8</v>
+      <c r="AE29" s="3">
+        <v>0</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>8</v>
@@ -3255,26 +3316,29 @@
       <c r="AJ29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AK29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL29" s="3">
         <v>567700</v>
       </c>
-      <c r="AL29" s="3">
+      <c r="AM29" s="3">
         <v>-200</v>
       </c>
-      <c r="AM29" s="3">
+      <c r="AN29" s="3">
         <v>1600</v>
       </c>
-      <c r="AN29" s="3">
+      <c r="AO29" s="3">
         <v>-600</v>
       </c>
-      <c r="AO29" s="3">
+      <c r="AP29" s="3">
         <v>-500</v>
       </c>
-      <c r="AP29" s="3">
+      <c r="AQ29" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3395,8 +3459,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3517,252 +3584,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E32" s="3">
         <v>2700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-35200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-8900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>4800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>1600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>12200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>2300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-8800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>9000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>3600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>8900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>3200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>52600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>57100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>59600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>50700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>55500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>50800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>58200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>50900</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>54600</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>57900</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>56300</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>66200</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>100900</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>68400</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>65100</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>38000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-6500</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>59600</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>67900</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>72100</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-22300</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-5900</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-12500</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-13100</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>-15200</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>-800</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>231700</v>
+      </c>
+      <c r="E33" s="3">
         <v>151300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>238300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-2927600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>428700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>121000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>287800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>199800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>427000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>207800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>103300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>430700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>342400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>72500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-590500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>216400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>47300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>151500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>80000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>453000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>388600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>84100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-1369800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>342800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>195000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-117000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>163700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-402800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>329400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>151400</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>76000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>338300</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>424100</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>278100</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>740900</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>286800</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>331500</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>207900</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>1455500</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>202500</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3883,257 +3959,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>231700</v>
+      </c>
+      <c r="E35" s="3">
         <v>151300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>238300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-2927600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>428700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>121000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>287800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>199800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>427000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>207800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>103300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>430700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>342400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>72500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-590500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>216400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>47300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>151500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>80000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>453000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>388600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>84100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-1369800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>342800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>195000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-117000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>163700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-402800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>329400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>151400</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>76000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>338300</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>424100</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>278100</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>740900</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>286800</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>331500</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>207900</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>1455500</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>202500</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4176,8 +4261,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4220,145 +4306,149 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2128100</v>
+      </c>
+      <c r="E41" s="3">
         <v>382600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>896500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>950200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>613800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>412700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>969300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1021700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1647300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>458400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>868900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>801700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>960900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>328200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>600000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>525200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>442100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>358700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>637400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>616300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1308900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>532700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>770100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>731300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>780800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>666100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>523400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>410200</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>490200</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>234400</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1057900</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>750100</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>792900</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>197900</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>418600</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>971300</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>502900</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>395000</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>560900</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>9981500</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
         <v>86900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>83700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>70800</v>
       </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
       <c r="H42" s="3">
         <v>0</v>
       </c>
@@ -4464,541 +4554,556 @@
       <c r="AP42" s="3">
         <v>0</v>
       </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1177800</v>
+      </c>
+      <c r="E43" s="3">
         <v>971900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>890300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>993800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1155400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>909000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>842900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1018100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1204600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1016200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>879400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1080400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1144200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>925400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>866200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>988700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1091700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>968500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>879400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>991600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1086700</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>717200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>687100</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>817300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>842800</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>744900</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>820300</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>950600</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>1108100</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1051100</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>871000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>1117600</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>1116000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>947300</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>902000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>1031300</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>1076700</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>923000</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>805300</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>638800</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>849100</v>
+      </c>
+      <c r="E44" s="3">
         <v>812800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>715900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>820600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>902000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>870500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>727800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>833300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>848500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>870900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>802300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>852600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>863400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>915600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>792900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>866800</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>872400</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>935800</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>804700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>806500</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>749500</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>746400</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>664300</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>657700</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>639100</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>681500</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>615900</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>642800</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>698100</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>687900</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>591800</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>631900</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>637500</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>665600</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>591500</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>636000</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>633700</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>663500</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>592700</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>218300</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>428500</v>
+      </c>
+      <c r="E45" s="3">
         <v>489600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>349100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>395000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>404900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>371400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>308400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>356400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>337300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>331500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>297900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>353100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>360700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>382400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>378900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>368700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>465700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>607600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>457200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>505500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>457000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>369600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>297300</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>434200</v>
-      </c>
-      <c r="AA45" s="3">
-        <v>280000</v>
       </c>
       <c r="AB45" s="3">
         <v>280000</v>
       </c>
       <c r="AC45" s="3">
+        <v>280000</v>
+      </c>
+      <c r="AD45" s="3">
         <v>224800</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>283300</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>304000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>364600</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>245600</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>312700</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>341100</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>326200</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>277600</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>277800</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>275700</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>297700</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>210700</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>109100</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4583500</v>
+      </c>
+      <c r="E46" s="3">
         <v>2743800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2935500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3230400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>3076100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2563600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2848400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3229500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>4037700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2677000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2848500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>3087800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>3329200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2551600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2638000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>2749400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>2871900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>2870600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>2778700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>2919900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>3602100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>2365900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>2418800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>2640500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>2542700</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>2372500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>2184400</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>2286900</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>2600400</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>2338000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>2766300</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>2812300</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>2887500</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>2137000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>2189700</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>2916400</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>2489000</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>2279200</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>2169600</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>10947700</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>262200</v>
+      </c>
+      <c r="E47" s="3">
         <v>246800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>255500</v>
       </c>
-      <c r="F47" s="3" t="s">
+      <c r="G47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>317400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>283000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>205200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>39200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>75000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>62600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>264300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>91900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>29300</v>
       </c>
-      <c r="P47" s="3" t="s">
+      <c r="Q47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
-      </c>
       <c r="R47" s="3">
         <v>0</v>
       </c>
@@ -5065,261 +5170,270 @@
       <c r="AM47" s="3">
         <v>0</v>
       </c>
-      <c r="AN47" s="3" t="s">
+      <c r="AN47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AO47" s="3">
-        <v>0</v>
-      </c>
       <c r="AP47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ47" s="3">
         <v>2661200</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4865700</v>
+      </c>
+      <c r="E48" s="3">
         <v>4895700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>4962700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>4823600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>4830200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>4702400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>4649400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4694700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>4674700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>4651500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>4645200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>4468000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>4542700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>4431000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>4355500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>4175900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>4298300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>4326500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>4311500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>4238600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>4307700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>4275200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>4386500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>4317700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>4484600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>4538400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>4701000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>4587000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>4662700</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>4707400</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>4608300</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>4593500</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>4599400</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>4680800</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>4673700</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>4590200</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>4585200</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>4528800</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>4507400</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>1527100</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>13984400</v>
+      </c>
+      <c r="E49" s="3">
         <v>13825700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>13935800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>13958500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>17986400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>17786800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>17777500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>17725600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>17715400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>17793600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>17939900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>18033000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>18103100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>18091700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>18092000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>18796500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>19142000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>19376800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>19439400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>19497400</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>19655200</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>19636100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>19707100</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>21034500</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>20945800</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>20844100</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>21287400</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>21136400</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>22056300</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>22029000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>22037200</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>22329400</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>22351000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>22680300</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>22702000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>22662700</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>22590800</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>22308800</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>22282000</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>6805600</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5440,8 +5554,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5562,130 +5679,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>663200</v>
+      </c>
+      <c r="E52" s="3">
         <v>655900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>586800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>860900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>616600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>594700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>505300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>946300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>891400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>887600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>517800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>887700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>785300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>778200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>782800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>986700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1075700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1147600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1089400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>987600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>954900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>886400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>818700</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>682600</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>665700</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>706100</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>687000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>741300</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>742200</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>749200</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>698000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>735100</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>723000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>686400</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>681500</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>508400</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>453600</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>426100</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>382500</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>255200</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5806,130 +5929,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>24359000</v>
+      </c>
+      <c r="E54" s="3">
         <v>22367900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>22738400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>22873400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>26826700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>25930500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>26064300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>26635300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>27394200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>26072300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>26375100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>26568400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>26789600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>25852500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>25868300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>26708500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>27387900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>27721500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>27619000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>27643500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>28519900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>27163600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>27331100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>28675300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>28638800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>28461100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>28859800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>28751600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>30061600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>29823600</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>30109800</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>30470300</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>30560900</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>30184500</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>30246900</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>30677700</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>30118600</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>29542900</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>29341500</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>22196800</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5972,8 +6101,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6016,740 +6146,759 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3112800</v>
+      </c>
+      <c r="E57" s="3">
         <v>2631500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1980500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2877100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3100600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2710000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2020100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3062200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3239500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2836900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1980800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3240600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3267400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2786100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2933600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>3045200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>3222400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2828800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>3061900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>3173200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>3318700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2485400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2842400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>3021300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>3145500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2409600</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>2683500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>2611800</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>3008100</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>2533900</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>2668300</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>2809800</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>2963000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>2518800</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>2670900</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>2482500</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>2601900</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>2190900</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>2320100</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>1268700</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2088500</v>
+      </c>
+      <c r="E58" s="3">
         <v>2477400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2486900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2461700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>117900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>136600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>78900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>85900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>942600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>954900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>958700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>926900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>472500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>458800</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>397100</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>505000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>247000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>681900</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>514900</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>559800</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1525100</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1063500</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1020100</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1242100</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>613000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1445000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>928200</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1193800</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1034700</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1641100</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1594500</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>1602000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>1411000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>1591300</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>1429600</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>1745000</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>686600</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>843000</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>684800</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>326900</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>10800</v>
+      </c>
+      <c r="E59" s="3">
         <v>15100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>170300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>6000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>22100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>19200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>210500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>100100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>54200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>71200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>329400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>70200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>90000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>61300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>44700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>41000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>44900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>44600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>45400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>46800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>48100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>47400</v>
-      </c>
-      <c r="Y59" s="3">
-        <v>47100</v>
       </c>
       <c r="Z59" s="3">
         <v>47100</v>
       </c>
       <c r="AA59" s="3">
+        <v>47100</v>
+      </c>
+      <c r="AB59" s="3">
         <v>47200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>148800</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>83800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>83000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>37500</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>27400</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>38100</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>10800</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>8000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>18300</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>18500</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>28700</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>19600</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>14800</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>152600</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>10100</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>5212100</v>
+      </c>
+      <c r="E60" s="3">
         <v>5124000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>5310800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>5344800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3240600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2865800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3045200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3248200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>4236300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3863000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>4092600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>4237700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3829900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>3306200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>3375400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>3591200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>3514300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>3555300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>3622200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>3779800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>4891900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>3596300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>3909600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>4310500</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>3805700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>4003400</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>3695500</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>3888600</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>4080300</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>4202400</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>4300900</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>4422600</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>4382000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>4128400</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>3399300</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>4256200</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>3308100</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>3048700</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>3157500</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>1605700</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>5825200</v>
+      </c>
+      <c r="E61" s="3">
         <v>4007900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4025500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4048100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>6421300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>6321300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>6275400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>6367500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>6326300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>5481700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>5476000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>5463100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>6357500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>6302300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>6165200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>6082700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>6557800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>6631500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>6647200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>6661000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>6701900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>7181200</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>7208200</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>7129500</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>8073700</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>8032100</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>8109500</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>8058500</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>8517900</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>8484800</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>8893800</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>8970300</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>9455100</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>9527000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>10598700</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>10574200</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>11185100</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>11443100</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>11387700</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>9560700</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>143300</v>
+      </c>
+      <c r="E62" s="3">
         <v>141400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>147600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>159300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>158800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>139400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>140900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>204000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>200400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>203300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>208400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>209800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>205200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>196400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3412500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3638100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>3713000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>3764200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>3685500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>3680200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>3689700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>3552100</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>3592000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>3459700</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>3491400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>3479600</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>3381700</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>3398000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>3318400</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>3248300</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>3179300</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>2987400</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>2927200</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>2865600</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>3074000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>3150700</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>3319600</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>3240800</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>3174600</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>1090000</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6870,8 +7019,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6992,8 +7144,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7114,130 +7269,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>13950300</v>
+      </c>
+      <c r="E66" s="3">
         <v>12002600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>12195700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>12204600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>13030000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>12478700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>12611600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>13067600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>13978500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>12714100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>12940000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>13080400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>13532700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>12933500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>13178600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>13538200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>14015100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>14189700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>14201900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>14368000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>15535100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>14582800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>14966100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>15162600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>15635900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>15774500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>15440400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>15589200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>16162200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>16176300</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>16602400</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>16606200</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>16984300</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>16738600</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>17268500</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>18189500</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>18022700</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>17944600</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>17922800</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>12277300</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7280,8 +7441,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7402,8 +7564,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7524,8 +7689,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7646,8 +7814,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7768,130 +7939,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>5925400</v>
+      </c>
+      <c r="E72" s="3">
         <v>5784300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>5723700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>5576500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>8597500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>8263000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>8238000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>8040200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>7932400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>7597400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>7484300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>7470000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>7129300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>6877000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>6894100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>7567400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>7433800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>7469800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>7401500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>7395800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>7016900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>6628300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>6544200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>7914000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>7571200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>7376200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>7617000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>7576800</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>8103100</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>7862400</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>7692900</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>7953200</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>7703500</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>7367900</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>6958400</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>6658700</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>6467000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>6232000</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>6119000</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>4768900</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8012,8 +8189,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8134,8 +8314,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8256,130 +8439,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>10119500</v>
+      </c>
+      <c r="E76" s="3">
         <v>10055800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>10230300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>10325100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>13440700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>13090300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>13092400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>13345300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>13179600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>13120100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>13196000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>13246000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>13030800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>12696500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>12689700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>13170300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>13372800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>13531800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>13417100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>13275500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>12984800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>12580800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>12365000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>13512700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>13002900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>12686600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>13419400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>13162400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>13899400</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>13647300</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>13507400</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>13864100</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>13576600</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>13445900</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>12978400</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>12488200</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>12095900</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>11598300</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>11418700</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>9919500</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8500,257 +8689,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>231700</v>
+      </c>
+      <c r="E81" s="3">
         <v>151300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>238300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-2927600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>428700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>121000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>287800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>199800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>427000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>207800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>103300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>430700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>342400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>72500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-590500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>216400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>47300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>151500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>80000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>453000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>388600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>84100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-1369800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>342800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>195000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-117000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>163700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-402800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>329400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>151400</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>76000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>338300</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>424100</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>278100</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>740900</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>286800</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>331500</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>207900</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>1455500</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>202500</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8793,130 +8991,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>118300</v>
+      </c>
+      <c r="E83" s="3">
         <v>111300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>102600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>124700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>115500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>116600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>121800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>116300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>117000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>120400</v>
-      </c>
-      <c r="M83" s="3">
-        <v>118400</v>
       </c>
       <c r="N83" s="3">
         <v>118400</v>
       </c>
       <c r="O83" s="3">
+        <v>118400</v>
+      </c>
+      <c r="P83" s="3">
         <v>119500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>120400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>169200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>170200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>171700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>173700</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>181900</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>200300</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>201600</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>202300</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>207100</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>220700</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>237700</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>256500</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>217600</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>211700</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>216800</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>212900</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>213300</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>214600</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>215900</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>213700</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>208500</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>208300</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>198900</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>197100</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>184100</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>66600</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9037,8 +9239,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9159,8 +9364,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9281,8 +9489,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9403,8 +9614,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9525,130 +9739,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>817900</v>
+      </c>
+      <c r="E89" s="3">
         <v>2500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>540700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>616100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>718300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-90700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>494500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>521200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>869200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>25400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>474500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>710100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>891000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>3400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>384500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>450700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>786100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-119300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>305800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>519200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>939400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-190900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>202500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>433300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1078000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-18100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>609100</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>460200</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>926500</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-98500</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>539900</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>493600</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>982600</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>315200</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>720900</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>326900</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>936800</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>-118300</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>496700</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>347800</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9691,130 +9911,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-103500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-231700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-182900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-133100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-163300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-237300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-111100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-170800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-177500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-214700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-177400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-159000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-153700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-181400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-130700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-142000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-144900</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-243800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-159200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-151500</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-109400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-102500</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-118400</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-111300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-120000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-225100</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-136500</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-146800</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-112500</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-198000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-160700</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-139900</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-142800</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-208300</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-133600</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-112000</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-174000</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-180000</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-494700</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>54300</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9935,8 +10159,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10057,130 +10284,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-369300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-230100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-187000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-135400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-158400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-341300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-117700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-148900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-168900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-212500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-173200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-327900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-163200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-177400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-120200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-135400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-143300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-226200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-156800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-153000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-115500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-84600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>37700</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-109800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-121500</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-220000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-114300</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-151200</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>26800</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-194600</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-135600</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-136300</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-145100</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-252100</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-140200</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-96100</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-169800</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-132100</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-12097700</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-128300</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10223,74 +10456,75 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>90100</v>
+      </c>
+      <c r="E96" s="3">
         <v>93600</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>90600</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>93000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>93500</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>99200</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>89800</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>91000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>91600</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>96800</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>88000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>88500</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>88700</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>89500</v>
-      </c>
-      <c r="Q96" s="3">
-        <v>-82200</v>
       </c>
       <c r="R96" s="3">
         <v>-82200</v>
       </c>
       <c r="S96" s="3">
+        <v>-82200</v>
+      </c>
+      <c r="T96" s="3">
         <v>-82500</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-82400</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-73900</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-73700</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-200</v>
       </c>
-      <c r="X96" s="3">
-        <v>0</v>
-      </c>
       <c r="Y96" s="3">
         <v>0</v>
       </c>
@@ -10298,31 +10532,31 @@
         <v>0</v>
       </c>
       <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-1900</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-123400</v>
-      </c>
-      <c r="AC96" s="3">
-        <v>-123500</v>
       </c>
       <c r="AD96" s="3">
         <v>-123500</v>
       </c>
       <c r="AE96" s="3">
-        <v>-88700</v>
+        <v>-123500</v>
       </c>
       <c r="AF96" s="3">
         <v>-88700</v>
       </c>
       <c r="AG96" s="3">
-        <v>-88600</v>
+        <v>-88700</v>
       </c>
       <c r="AH96" s="3">
         <v>-88600</v>
       </c>
       <c r="AI96" s="3">
-        <v>-88500</v>
+        <v>-88600</v>
       </c>
       <c r="AJ96" s="3">
         <v>-88500</v>
@@ -10331,7 +10565,7 @@
         <v>-88500</v>
       </c>
       <c r="AL96" s="3">
-        <v>-88300</v>
+        <v>-88500</v>
       </c>
       <c r="AM96" s="3">
         <v>-88300</v>
@@ -10343,10 +10577,13 @@
         <v>-88300</v>
       </c>
       <c r="AP96" s="3">
+        <v>-88300</v>
+      </c>
+      <c r="AQ96" s="3">
         <v>-88100</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10467,8 +10704,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10589,8 +10829,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10711,370 +10954,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1309100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-282200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-410200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-140400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-375000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-131200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-393600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1030400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>501800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-216200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-252800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-526700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-99400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-102500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-216700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-203000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-542300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>72500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-122600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-1045700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-48900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>45000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-229100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-391500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-848500</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>398700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-393400</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-377700</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-701100</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-534800</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-85500</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-398700</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-234800</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-289900</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-1128600</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>225400</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-673500</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>80300</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>2197800</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>6763500</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>16200</v>
+      </c>
+      <c r="E101" s="3">
         <v>6600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-35600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>32500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-13200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-7200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>18700</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-14700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>4300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>4700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>27200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-29200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-17100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-5700</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>27200</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-29200</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-17100</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-5700</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-5300</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-13100</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>1200</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-6900</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>27700</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>18500</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>6700</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-17900</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>11800</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-11300</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>3600</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>4400</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-11000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-1400</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-7700</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>6100</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-4800</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>12200</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>14400</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>4200</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-17400</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>-9800</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1745500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-513900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-53700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>336400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>201100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-556600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-52400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-625600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1188900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-410500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>67200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-159200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>632700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-271800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>74800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>83100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>83400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-278700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>21100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-692600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>776200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-237400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>38800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-49500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>114700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>142700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>113200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-80000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>255800</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-823500</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>307800</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-42800</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>595000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-220700</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-552700</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>468400</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>107900</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-165900</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-9420600</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>6991200</v>
       </c>
     </row>
